--- a/input/dataset/urls.xlsx
+++ b/input/dataset/urls.xlsx
@@ -409,7 +409,7 @@
         <v>https://airtel.black</v>
       </c>
       <c r="B2" t="str">
-        <v>need to retrain</v>
+        <v/>
       </c>
     </row>
     <row r="3">
